--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="D2">
-        <v>221</v>
+        <v>364</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="D3">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
@@ -430,13 +430,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D2">
         <v>364</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -450,10 +450,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D3">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E3">
         <v>0</v>
